--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6142" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6142" uniqueCount="710">
   <si>
     <t>Property</t>
   </si>
@@ -1651,6 +1651,9 @@
   <si>
     <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_DentalOral_BodyStructure_BodyLandmarkOrientation}
 </t>
+  </si>
+  <si>
+    <t>JP Observation DentalOral BodyStructure BodyLandmarkOrientation</t>
   </si>
   <si>
     <t>Observation.bodySite.extension:bodyStructure.extension:includedStructure.extension:qualifier</t>
@@ -15113,7 +15116,7 @@
         <v>527</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="M105" t="s" s="2">
         <v>447</v>
@@ -15202,13 +15205,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>506</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>83</v>
@@ -15230,13 +15233,13 @@
         <v>83</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15322,7 +15325,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B107" t="s" s="2">
         <v>512</v>
@@ -15440,7 +15443,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>514</v>
@@ -15558,7 +15561,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>516</v>
@@ -15601,7 +15604,7 @@
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>83</v>
@@ -15678,7 +15681,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B110" t="s" s="2">
         <v>519</v>
@@ -15796,10 +15799,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15914,10 +15917,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16034,10 +16037,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16109,7 +16112,7 @@
         <v>83</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AC113" s="2"/>
       <c r="AD113" t="s" s="2">
@@ -16154,13 +16157,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>83</v>
@@ -16185,10 +16188,10 @@
         <v>221</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>224</v>
@@ -16223,7 +16226,7 @@
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
@@ -16276,10 +16279,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16394,10 +16397,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16514,10 +16517,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16559,7 +16562,7 @@
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>83</v>
@@ -16636,10 +16639,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16756,10 +16759,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16876,10 +16879,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16996,10 +16999,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17118,13 +17121,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>83</v>
@@ -17149,10 +17152,10 @@
         <v>221</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>224</v>
@@ -17187,7 +17190,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>83</v>
@@ -17240,10 +17243,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17358,10 +17361,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17478,10 +17481,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17523,7 +17526,7 @@
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>83</v>
@@ -17600,10 +17603,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17720,10 +17723,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17840,10 +17843,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17960,10 +17963,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18082,10 +18085,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18204,10 +18207,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18247,7 +18250,7 @@
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>83</v>
@@ -18324,10 +18327,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18350,7 +18353,7 @@
         <v>83</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L132" t="s" s="2">
         <v>465</v>
@@ -18442,7 +18445,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>457</v>
@@ -18485,7 +18488,7 @@
       </c>
       <c r="Q133" s="2"/>
       <c r="R133" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S133" t="s" s="2">
         <v>83</v>
@@ -18562,7 +18565,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>464</v>
@@ -18588,7 +18591,7 @@
         <v>83</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L134" t="s" s="2">
         <v>465</v>
@@ -18680,10 +18683,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18802,10 +18805,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18924,10 +18927,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18953,16 +18956,16 @@
         <v>191</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>83</v>
@@ -18990,10 +18993,10 @@
         <v>326</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>83</v>
@@ -19011,7 +19014,7 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -19032,10 +19035,10 @@
         <v>83</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>83</v>
@@ -19046,10 +19049,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19072,16 +19075,16 @@
         <v>83</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -19131,7 +19134,7 @@
         <v>83</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -19149,27 +19152,27 @@
         <v>83</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19192,16 +19195,16 @@
         <v>83</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19251,7 +19254,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -19269,27 +19272,27 @@
         <v>83</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19312,19 +19315,19 @@
         <v>83</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>83</v>
@@ -19373,7 +19376,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -19385,7 +19388,7 @@
         <v>83</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>83</v>
@@ -19394,10 +19397,10 @@
         <v>83</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>83</v>
@@ -19408,10 +19411,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19526,10 +19529,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19646,14 +19649,14 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -19675,10 +19678,10 @@
         <v>140</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N143" t="s" s="2">
         <v>143</v>
@@ -19733,7 +19736,7 @@
         <v>83</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -19768,10 +19771,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19794,13 +19797,13 @@
         <v>83</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -19851,7 +19854,7 @@
         <v>83</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -19860,7 +19863,7 @@
         <v>94</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>106</v>
@@ -19872,10 +19875,10 @@
         <v>83</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>83</v>
@@ -19886,10 +19889,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19912,13 +19915,13 @@
         <v>83</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -19969,7 +19972,7 @@
         <v>83</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -19978,7 +19981,7 @@
         <v>94</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>106</v>
@@ -19990,10 +19993,10 @@
         <v>83</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>83</v>
@@ -20004,10 +20007,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20033,16 +20036,16 @@
         <v>191</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>83</v>
@@ -20070,10 +20073,10 @@
         <v>118</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>83</v>
@@ -20091,7 +20094,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -20109,10 +20112,10 @@
         <v>83</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>426</v>
@@ -20126,10 +20129,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20155,16 +20158,16 @@
         <v>191</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>83</v>
@@ -20192,10 +20195,10 @@
         <v>326</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>83</v>
@@ -20213,7 +20216,7 @@
         <v>83</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -20231,10 +20234,10 @@
         <v>83</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>426</v>
@@ -20248,10 +20251,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20274,17 +20277,17 @@
         <v>83</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>83</v>
@@ -20333,7 +20336,7 @@
         <v>83</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
@@ -20357,7 +20360,7 @@
         <v>83</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>83</v>
@@ -20368,10 +20371,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20397,10 +20400,10 @@
         <v>208</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20451,7 +20454,7 @@
         <v>83</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -20472,10 +20475,10 @@
         <v>83</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>83</v>
@@ -20486,10 +20489,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20512,16 +20515,16 @@
         <v>95</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20571,7 +20574,7 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -20592,10 +20595,10 @@
         <v>83</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>83</v>
@@ -20606,10 +20609,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20632,16 +20635,16 @@
         <v>95</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20691,7 +20694,7 @@
         <v>83</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -20712,10 +20715,10 @@
         <v>83</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>83</v>
@@ -20726,10 +20729,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20752,19 +20755,19 @@
         <v>95</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>83</v>
@@ -20813,7 +20816,7 @@
         <v>83</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -20834,10 +20837,10 @@
         <v>83</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>83</v>
@@ -20848,10 +20851,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20966,10 +20969,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21086,14 +21089,14 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -21115,10 +21118,10 @@
         <v>140</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N155" t="s" s="2">
         <v>143</v>
@@ -21173,7 +21176,7 @@
         <v>83</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21208,10 +21211,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21237,13 +21240,13 @@
         <v>191</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="O156" t="s" s="2">
         <v>325</v>
@@ -21295,7 +21298,7 @@
         <v>83</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>94</v>
@@ -21313,7 +21316,7 @@
         <v>83</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>331</v>
@@ -21330,10 +21333,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21356,16 +21359,16 @@
         <v>95</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="O157" t="s" s="2">
         <v>402</v>
@@ -21417,7 +21420,7 @@
         <v>83</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -21435,7 +21438,7 @@
         <v>83</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>405</v>
@@ -21452,10 +21455,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21481,13 +21484,13 @@
         <v>191</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="O158" t="s" s="2">
         <v>411</v>
@@ -21539,7 +21542,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -21574,10 +21577,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21603,16 +21606,16 @@
         <v>191</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>83</v>
@@ -21661,7 +21664,7 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -21696,10 +21699,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21725,16 +21728,16 @@
         <v>84</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>83</v>
@@ -21783,7 +21786,7 @@
         <v>83</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -21804,10 +21807,10 @@
         <v>83</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6142" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6142" uniqueCount="713">
   <si>
     <t>Property</t>
   </si>
@@ -1575,6 +1575,9 @@
     <t>JP Observation DentalOral BodyStructure IncludedStructure</t>
   </si>
   <si>
+    <t>内部に含まれる構造の拡張</t>
+  </si>
+  <si>
     <t>Observation.bodySite.extension:bodyStructure.extension:includedStructure.id</t>
   </si>
   <si>
@@ -1643,6 +1646,9 @@
     <t>JP Observation DentalOral BodyStructure Laterality</t>
   </si>
   <si>
+    <t>左右をあらわす拡張</t>
+  </si>
+  <si>
     <t>Observation.bodySite.extension:bodyStructure.extension:includedStructure.extension:bodyLandmarkOrientation</t>
   </si>
   <si>
@@ -1654,6 +1660,9 @@
   </si>
   <si>
     <t>JP Observation DentalOral BodyStructure BodyLandmarkOrientation</t>
+  </si>
+  <si>
+    <t>ランドマークに関する拡張</t>
   </si>
   <si>
     <t>Observation.bodySite.extension:bodyStructure.extension:includedStructure.extension:qualifier</t>
@@ -14051,7 +14060,7 @@
         <v>502</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -14137,10 +14146,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14255,10 +14264,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14373,13 +14382,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B99" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="B99" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="C99" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>83</v>
@@ -14401,13 +14410,13 @@
         <v>83</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14493,10 +14502,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14611,10 +14620,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14729,10 +14738,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14772,7 +14781,7 @@
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>83</v>
@@ -14849,10 +14858,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14912,7 +14921,7 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>83</v>
@@ -14965,13 +14974,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>83</v>
@@ -14993,13 +15002,13 @@
         <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>447</v>
+        <v>526</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15085,13 +15094,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>83</v>
@@ -15113,13 +15122,13 @@
         <v>83</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>447</v>
+        <v>531</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15205,13 +15214,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>83</v>
@@ -15233,13 +15242,13 @@
         <v>83</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15325,10 +15334,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15443,10 +15452,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15561,10 +15570,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15604,7 +15613,7 @@
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="S109" t="s" s="2">
         <v>83</v>
@@ -15681,10 +15690,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15799,10 +15808,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15917,10 +15926,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16037,10 +16046,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16112,7 +16121,7 @@
         <v>83</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="AC113" s="2"/>
       <c r="AD113" t="s" s="2">
@@ -16157,13 +16166,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D114" t="s" s="2">
         <v>83</v>
@@ -16188,10 +16197,10 @@
         <v>221</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>224</v>
@@ -16226,7 +16235,7 @@
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>83</v>
@@ -16279,10 +16288,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16397,10 +16406,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16517,10 +16526,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16562,7 +16571,7 @@
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>83</v>
@@ -16639,10 +16648,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16759,10 +16768,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16879,10 +16888,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16999,10 +17008,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17121,13 +17130,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D122" t="s" s="2">
         <v>83</v>
@@ -17152,10 +17161,10 @@
         <v>221</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>224</v>
@@ -17190,7 +17199,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>83</v>
@@ -17243,10 +17252,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17361,10 +17370,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17481,10 +17490,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17526,7 +17535,7 @@
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="S125" t="s" s="2">
         <v>83</v>
@@ -17603,10 +17612,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17723,10 +17732,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17843,10 +17852,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17963,10 +17972,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18085,10 +18094,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18207,10 +18216,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18250,7 +18259,7 @@
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>83</v>
@@ -18327,10 +18336,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18353,7 +18362,7 @@
         <v>83</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="L132" t="s" s="2">
         <v>465</v>
@@ -18445,7 +18454,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>457</v>
@@ -18488,7 +18497,7 @@
       </c>
       <c r="Q133" s="2"/>
       <c r="R133" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="S133" t="s" s="2">
         <v>83</v>
@@ -18565,7 +18574,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>464</v>
@@ -18591,7 +18600,7 @@
         <v>83</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="L134" t="s" s="2">
         <v>465</v>
@@ -18683,10 +18692,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18805,10 +18814,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18927,10 +18936,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18956,16 +18965,16 @@
         <v>191</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>83</v>
@@ -18993,10 +19002,10 @@
         <v>326</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>83</v>
@@ -19014,7 +19023,7 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -19035,10 +19044,10 @@
         <v>83</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>83</v>
@@ -19049,10 +19058,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19075,16 +19084,16 @@
         <v>83</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -19134,7 +19143,7 @@
         <v>83</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -19152,27 +19161,27 @@
         <v>83</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19195,16 +19204,16 @@
         <v>83</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -19254,7 +19263,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -19272,27 +19281,27 @@
         <v>83</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19315,19 +19324,19 @@
         <v>83</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>83</v>
@@ -19376,7 +19385,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -19388,7 +19397,7 @@
         <v>83</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="AK140" t="s" s="2">
         <v>83</v>
@@ -19397,10 +19406,10 @@
         <v>83</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>83</v>
@@ -19411,10 +19420,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19529,10 +19538,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19649,14 +19658,14 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -19678,10 +19687,10 @@
         <v>140</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="N143" t="s" s="2">
         <v>143</v>
@@ -19736,7 +19745,7 @@
         <v>83</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -19771,10 +19780,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19797,13 +19806,13 @@
         <v>83</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -19854,7 +19863,7 @@
         <v>83</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -19863,7 +19872,7 @@
         <v>94</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>106</v>
@@ -19875,10 +19884,10 @@
         <v>83</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>83</v>
@@ -19889,10 +19898,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19915,13 +19924,13 @@
         <v>83</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -19972,16 +19981,16 @@
         <v>83</v>
       </c>
       <c r="AF145" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI145" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="AG145" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH145" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI145" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>106</v>
@@ -19993,10 +20002,10 @@
         <v>83</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>83</v>
@@ -20007,10 +20016,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -20036,16 +20045,16 @@
         <v>191</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>83</v>
@@ -20073,10 +20082,10 @@
         <v>118</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>83</v>
@@ -20094,7 +20103,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -20112,10 +20121,10 @@
         <v>83</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>426</v>
@@ -20129,10 +20138,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20158,16 +20167,16 @@
         <v>191</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>83</v>
@@ -20195,10 +20204,10 @@
         <v>326</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>83</v>
@@ -20216,7 +20225,7 @@
         <v>83</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -20234,10 +20243,10 @@
         <v>83</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>426</v>
@@ -20251,10 +20260,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20277,17 +20286,17 @@
         <v>83</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>83</v>
@@ -20336,7 +20345,7 @@
         <v>83</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
@@ -20360,7 +20369,7 @@
         <v>83</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>83</v>
@@ -20371,10 +20380,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20400,10 +20409,10 @@
         <v>208</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -20454,7 +20463,7 @@
         <v>83</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -20475,10 +20484,10 @@
         <v>83</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>83</v>
@@ -20489,10 +20498,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20515,16 +20524,16 @@
         <v>95</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -20574,7 +20583,7 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -20595,10 +20604,10 @@
         <v>83</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>83</v>
@@ -20609,10 +20618,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20635,16 +20644,16 @@
         <v>95</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -20694,7 +20703,7 @@
         <v>83</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -20715,10 +20724,10 @@
         <v>83</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>83</v>
@@ -20729,10 +20738,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20755,19 +20764,19 @@
         <v>95</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>83</v>
@@ -20816,7 +20825,7 @@
         <v>83</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -20837,10 +20846,10 @@
         <v>83</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>83</v>
@@ -20851,10 +20860,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20969,10 +20978,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21089,14 +21098,14 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -21118,10 +21127,10 @@
         <v>140</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="N155" t="s" s="2">
         <v>143</v>
@@ -21176,7 +21185,7 @@
         <v>83</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21211,10 +21220,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21240,13 +21249,13 @@
         <v>191</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="O156" t="s" s="2">
         <v>325</v>
@@ -21298,7 +21307,7 @@
         <v>83</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>94</v>
@@ -21316,7 +21325,7 @@
         <v>83</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>331</v>
@@ -21333,10 +21342,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21359,16 +21368,16 @@
         <v>95</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="O157" t="s" s="2">
         <v>402</v>
@@ -21420,7 +21429,7 @@
         <v>83</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -21438,7 +21447,7 @@
         <v>83</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>405</v>
@@ -21455,10 +21464,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21484,13 +21493,13 @@
         <v>191</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="O158" t="s" s="2">
         <v>411</v>
@@ -21542,7 +21551,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -21577,10 +21586,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21606,16 +21615,16 @@
         <v>191</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>83</v>
@@ -21664,7 +21673,7 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -21699,10 +21708,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21728,16 +21737,16 @@
         <v>84</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>83</v>
@@ -21786,7 +21795,7 @@
         <v>83</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -21807,10 +21816,10 @@
         <v>83</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -1772,7 +1772,7 @@
     <t>観測は値を持つように存在しますが、それが誤っている場合、または観測のグループを表す場合はそうではありません。 / An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_DentalPresentTeethObservation_CS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalPresentTeethObservation_VS</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7

--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7034" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7035" uniqueCount="732">
   <si>
     <t>Property</t>
   </si>
@@ -6477,7 +6477,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>94</v>
@@ -7550,7 +7550,7 @@
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>94</v>
@@ -8144,7 +8144,7 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>94</v>
@@ -8738,7 +8738,7 @@
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>83</v>
@@ -8967,11 +8967,11 @@
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>82</v>
@@ -8989,12 +8989,14 @@
         <v>139</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>140</v>
+        <v>181</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>182</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -9067,7 +9069,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -9091,10 +9093,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>83</v>
@@ -9565,7 +9567,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>94</v>
@@ -9926,7 +9928,7 @@
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>83</v>
@@ -10397,7 +10399,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>94</v>
@@ -11229,7 +11231,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>94</v>

--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-ecs.xlsx
@@ -7069,7 +7069,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>94</v>
